--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\GitHub\bgl-scada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BA7D42-A527-45DF-9317-2D033A50905B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74633D34-6C51-4641-ACBA-3AF4CED4183F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3576" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3578" uniqueCount="798">
   <si>
     <t>Parent ID</t>
   </si>
@@ -26068,7 +26068,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -27433,32 +27433,32 @@
         <v>19</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C124" s="6">
-        <v>46295.859201388892</v>
+        <v>206</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46286.43283366898</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="C125" s="6">
-        <v>46295.860023148147</v>
+        <v>46295.859201388892</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C126" s="6">
-        <v>46295.860532407409</v>
+        <v>46295.860023148147</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27466,10 +27466,10 @@
         <v>111</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C127" s="6">
-        <v>46295.860810185186</v>
+        <v>46295.860532407409</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27477,32 +27477,32 @@
         <v>111</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C128" s="6">
-        <v>46295.861157407409</v>
+        <v>46295.860810185186</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C129" s="6">
-        <v>46295.861863425926</v>
+        <v>46295.861157407409</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="C130" s="6">
-        <v>46295.862500000003</v>
+        <v>46295.861863425926</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27510,10 +27510,10 @@
         <v>116</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C131" s="6">
-        <v>46295.862928240742</v>
+        <v>46295.862500000003</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27521,10 +27521,10 @@
         <v>116</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C132" s="6">
-        <v>46295.863425925927</v>
+        <v>46295.862928240742</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27532,10 +27532,10 @@
         <v>116</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C133" s="6">
-        <v>46295.863807870373</v>
+        <v>46295.863425925927</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27543,43 +27543,43 @@
         <v>116</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C134" s="6">
-        <v>46295.864745370367</v>
+        <v>46295.863807870373</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B135" s="1">
-        <v>21300013</v>
-      </c>
       <c r="C135" s="6">
-        <v>46295.865428240744</v>
+        <v>46295.864745370367</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>126</v>
+      <c r="B136" s="1">
+        <v>21300013</v>
       </c>
       <c r="C136" s="6">
-        <v>46295.866076388891</v>
+        <v>46295.865428240744</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B137" s="1">
-        <v>21300001</v>
-      </c>
       <c r="C137" s="6">
-        <v>46295.867893518516</v>
+        <v>46295.866076388891</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27587,10 +27587,10 @@
         <v>126</v>
       </c>
       <c r="B138" s="1">
-        <v>21300018</v>
+        <v>21300001</v>
       </c>
       <c r="C138" s="6">
-        <v>46295.868171296293</v>
+        <v>46295.867893518516</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27598,10 +27598,10 @@
         <v>126</v>
       </c>
       <c r="B139" s="1">
-        <v>21300085</v>
+        <v>21300018</v>
       </c>
       <c r="C139" s="6">
-        <v>46295.872430555559</v>
+        <v>46295.868171296293</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27609,10 +27609,10 @@
         <v>126</v>
       </c>
       <c r="B140" s="1">
-        <v>21300044</v>
+        <v>21300085</v>
       </c>
       <c r="C140" s="6">
-        <v>46295.873055555552</v>
+        <v>46295.872430555559</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27620,21 +27620,21 @@
         <v>126</v>
       </c>
       <c r="B141" s="1">
-        <v>21300064</v>
+        <v>21300044</v>
       </c>
       <c r="C141" s="6">
-        <v>46295.873541666668</v>
+        <v>46295.873055555552</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>127</v>
+      <c r="B142" s="1">
+        <v>21300064</v>
       </c>
       <c r="C142" s="6">
-        <v>46295.873969907407</v>
+        <v>46295.873541666668</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27642,21 +27642,21 @@
         <v>126</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C143" s="6">
-        <v>46295.874305555553</v>
+        <v>46295.873969907407</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B144" s="1">
-        <v>31000104</v>
+        <v>126</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C144" s="6">
-        <v>46295.875740740739</v>
+        <v>46295.874305555553</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -27664,40 +27664,40 @@
         <v>130</v>
       </c>
       <c r="B145" s="1">
-        <v>31000088</v>
+        <v>31000104</v>
       </c>
       <c r="C145" s="6">
-        <v>46295.876898148148</v>
+        <v>46295.875740740739</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>132</v>
+      <c r="B146" s="1">
+        <v>31000088</v>
       </c>
       <c r="C146" s="6">
-        <v>46295.878194444442</v>
+        <v>46295.876898148148</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C147" s="6">
         <v>46295.878194444442</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="C148" s="6">
         <v>46295.878194444442</v>
@@ -27705,10 +27705,10 @@
     </row>
     <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C149" s="6">
         <v>46295.878194444442</v>
@@ -27716,10 +27716,10 @@
     </row>
     <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>796</v>
+        <v>240</v>
       </c>
       <c r="C150" s="6">
         <v>46295.878194444442</v>
@@ -27727,10 +27727,10 @@
     </row>
     <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>241</v>
+        <v>796</v>
       </c>
       <c r="C151" s="6">
         <v>46295.878194444442</v>
@@ -27738,12 +27738,23 @@
     </row>
     <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C152" s="6">
+        <v>46295.878194444442</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C153" s="6">
         <v>46295.878194444442</v>
       </c>
     </row>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\GitHub\bgl-scada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74633D34-6C51-4641-ACBA-3AF4CED4183F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70FD6E1-3704-41AE-A064-2673B8B42A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3578" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3576" uniqueCount="798">
   <si>
     <t>Parent ID</t>
   </si>
@@ -2455,7 +2455,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="dd&quot;/&quot;mm"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2511,6 +2511,14 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2559,7 +2567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2631,6 +2639,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -26068,10 +26077,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
     <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27452,9 +27462,9 @@
     </row>
     <row r="126" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B126" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B126" s="29" t="s">
         <v>111</v>
       </c>
       <c r="C126" s="6">
@@ -27692,12 +27702,12 @@
         <v>46295.878194444442</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="C148" s="6">
         <v>46295.878194444442</v>
@@ -27705,10 +27715,10 @@
     </row>
     <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C149" s="6">
         <v>46295.878194444442</v>
@@ -27716,10 +27726,10 @@
     </row>
     <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>240</v>
+        <v>796</v>
       </c>
       <c r="C150" s="6">
         <v>46295.878194444442</v>
@@ -27727,10 +27737,10 @@
     </row>
     <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>796</v>
+        <v>241</v>
       </c>
       <c r="C151" s="6">
         <v>46295.878194444442</v>
@@ -27738,28 +27748,18 @@
     </row>
     <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>149</v>
+        <v>795</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>241</v>
+        <v>797</v>
       </c>
       <c r="C152" s="6">
-        <v>46295.878194444442</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C153" s="6">
         <v>46295.878194444442</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>